--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,6 +1369,317 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124956639</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bukölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>493691</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6865197</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124956712</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58016</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102995</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Buskskvätta</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Saxicola rubetra</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bukölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>493628</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6865316</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124956490</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493891</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6864972</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124956639</v>
+        <v>124956490</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493691</v>
+        <v>493891</v>
       </c>
       <c r="R8" t="n">
-        <v>6865197</v>
+        <v>6864972</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,12 +1461,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956490</v>
+        <v>124956639</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,37 +1596,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493891</v>
+        <v>493691</v>
       </c>
       <c r="R10" t="n">
-        <v>6864972</v>
+        <v>6865197</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124956490</v>
+        <v>124956639</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493891</v>
+        <v>493691</v>
       </c>
       <c r="R8" t="n">
-        <v>6864972</v>
+        <v>6865197</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124956712</v>
+        <v>124956490</v>
       </c>
       <c r="B9" t="n">
-        <v>58016</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102995</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493628</v>
+        <v>493891</v>
       </c>
       <c r="R9" t="n">
-        <v>6865316</v>
+        <v>6864972</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1568,22 +1563,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956639</v>
+        <v>124956712</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>58016</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,37 +1591,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493691</v>
+        <v>493628</v>
       </c>
       <c r="R10" t="n">
-        <v>6865197</v>
+        <v>6865316</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124956639</v>
+        <v>124956712</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>58016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,37 +1387,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493691</v>
+        <v>493628</v>
       </c>
       <c r="R8" t="n">
-        <v>6865197</v>
+        <v>6865316</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1575,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956712</v>
+        <v>124956639</v>
       </c>
       <c r="B10" t="n">
-        <v>58016</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,42 +1596,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102995</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493628</v>
+        <v>493691</v>
       </c>
       <c r="R10" t="n">
-        <v>6865316</v>
+        <v>6865197</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124956712</v>
+        <v>124956639</v>
       </c>
       <c r="B8" t="n">
-        <v>58016</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,42 +1387,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102995</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493628</v>
+        <v>493691</v>
       </c>
       <c r="R8" t="n">
-        <v>6865316</v>
+        <v>6865197</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124956490</v>
+        <v>124956712</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>58016</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1489,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493891</v>
+        <v>493628</v>
       </c>
       <c r="R9" t="n">
-        <v>6864972</v>
+        <v>6865316</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1568,22 +1568,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956639</v>
+        <v>124956490</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,37 +1596,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493691</v>
+        <v>493891</v>
       </c>
       <c r="R10" t="n">
-        <v>6865197</v>
+        <v>6864972</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124956639</v>
+        <v>124956490</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493691</v>
+        <v>493891</v>
       </c>
       <c r="R8" t="n">
-        <v>6865197</v>
+        <v>6864972</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124956712</v>
+        <v>124956639</v>
       </c>
       <c r="B9" t="n">
-        <v>58016</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,42 +1489,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102995</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493628</v>
+        <v>493691</v>
       </c>
       <c r="R9" t="n">
-        <v>6865316</v>
+        <v>6865197</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956490</v>
+        <v>124956712</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>58016</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,34 +1591,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493891</v>
+        <v>493628</v>
       </c>
       <c r="R10" t="n">
-        <v>6864972</v>
+        <v>6865316</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124956490</v>
+        <v>124956712</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>58016</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,34 +1387,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>102995</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493891</v>
+        <v>493628</v>
       </c>
       <c r="R8" t="n">
-        <v>6864972</v>
+        <v>6865316</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1461,12 +1466,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1575,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956712</v>
+        <v>124956490</v>
       </c>
       <c r="B10" t="n">
-        <v>58016</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,39 +1596,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102995</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493628</v>
+        <v>493891</v>
       </c>
       <c r="R10" t="n">
-        <v>6865316</v>
+        <v>6864972</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124956639</v>
+        <v>124956490</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,37 +1494,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493691</v>
+        <v>493891</v>
       </c>
       <c r="R9" t="n">
-        <v>6865197</v>
+        <v>6864972</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,22 +1568,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956490</v>
+        <v>124956639</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,37 +1596,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493891</v>
+        <v>493691</v>
       </c>
       <c r="R10" t="n">
-        <v>6864972</v>
+        <v>6865197</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,12 +1670,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124956712</v>
+        <v>124956490</v>
       </c>
       <c r="B8" t="n">
-        <v>58016</v>
+        <v>80028</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,39 +1387,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102995</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493628</v>
+        <v>493891</v>
       </c>
       <c r="R8" t="n">
-        <v>6865316</v>
+        <v>6864972</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1466,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124956490</v>
+        <v>124956639</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,37 +1489,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493891</v>
+        <v>493691</v>
       </c>
       <c r="R9" t="n">
-        <v>6864972</v>
+        <v>6865197</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,22 +1563,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956639</v>
+        <v>124956712</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>58134</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,37 +1591,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493691</v>
+        <v>493628</v>
       </c>
       <c r="R10" t="n">
-        <v>6865197</v>
+        <v>6865316</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124956639</v>
+        <v>124956712</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>58134</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,37 +1489,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102995</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493691</v>
+        <v>493628</v>
       </c>
       <c r="R9" t="n">
-        <v>6865197</v>
+        <v>6865316</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1575,10 +1580,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956712</v>
+        <v>124956639</v>
       </c>
       <c r="B10" t="n">
-        <v>58134</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,42 +1596,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102995</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493628</v>
+        <v>493691</v>
       </c>
       <c r="R10" t="n">
-        <v>6865316</v>
+        <v>6865197</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>

--- a/artfynd/A 38530-2019 artfynd.xlsx
+++ b/artfynd/A 38530-2019 artfynd.xlsx
@@ -1371,15 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124956490</v>
+        <v>124956639</v>
       </c>
       <c r="B8" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,37 +1382,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>493891</v>
+        <v>493691</v>
       </c>
       <c r="R8" t="n">
-        <v>6864972</v>
+        <v>6865197</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,12 +1456,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1478,11 +1473,6 @@
       <c r="B9" t="n">
         <v>58134</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>NT</t>
@@ -1580,15 +1570,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124956639</v>
+        <v>124956490</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,37 +1581,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bukölsmyran, Hls</t>
+          <t>Bukölsmyran, Bukölsmyran, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>493691</v>
+        <v>493891</v>
       </c>
       <c r="R10" t="n">
-        <v>6865197</v>
+        <v>6864972</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1670,12 +1655,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
